--- a/结果/1.识别结果/【人教版】一年级下册(2025春版)道德与法治电子课本_独立职业.xlsx
+++ b/结果/1.识别结果/【人教版】一年级下册(2025春版)道德与法治电子课本_独立职业.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -565,7 +565,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
       <c r="F102" t="n">
